--- a/Producer - Product Mapping - Copy.xlsx
+++ b/Producer - Product Mapping - Copy.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30117"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="214" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B9DA81B-13AC-4446-B40F-B1813AD3B867}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grandcruliquidassetscom-my.sharepoint.com/personal/chang_grandcruliquidassets_com/Documents/Desktop/Email campaign dashboard/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="259" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C71AA76-B959-4952-AA42-F1EB9413484A}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47895" yWindow="0" windowWidth="19410" windowHeight="20985" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Producer - Tier" sheetId="1" r:id="rId1"/>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="221">
   <si>
     <t>First Growth Producers - Flagship</t>
   </si>
@@ -49,6 +54,9 @@
     <t>Second Label</t>
   </si>
   <si>
+    <t>Blue-chip Burgundy Producer</t>
+  </si>
+  <si>
     <t>Lafite</t>
   </si>
   <si>
@@ -64,6 +72,9 @@
     <t>Harlan Maiden</t>
   </si>
   <si>
+    <t>Domaine Dujac</t>
+  </si>
+  <si>
     <t>Latour</t>
   </si>
   <si>
@@ -79,384 +90,453 @@
     <t>Carruades de Lafite</t>
   </si>
   <si>
+    <t>Domaine de la Romanée-Conti (DRC)</t>
+  </si>
+  <si>
+    <t>Haut Brion (including Haut Brion-Blanc)</t>
+  </si>
+  <si>
+    <t>Bryant Family</t>
+  </si>
+  <si>
+    <t>Gruaud Larose</t>
+  </si>
+  <si>
+    <t>Tignanello</t>
+  </si>
+  <si>
+    <t>Le Petit Mouton</t>
+  </si>
+  <si>
+    <t>Bonneau du Martray</t>
+  </si>
+  <si>
+    <t>Mouton</t>
+  </si>
+  <si>
+    <t>Dalla Valle</t>
+  </si>
+  <si>
+    <t>Cos d'Estournel</t>
+  </si>
+  <si>
+    <t>Solaia</t>
+  </si>
+  <si>
+    <t>Le Petit Cheval</t>
+  </si>
+  <si>
+    <t>Mugnier Bonnes Mares</t>
+  </si>
+  <si>
+    <t>Margaux</t>
+  </si>
+  <si>
+    <t>Colgin Cellars</t>
+  </si>
+  <si>
+    <t>La Mission Haut-Brion</t>
+  </si>
+  <si>
+    <t>Guado al Tasso</t>
+  </si>
+  <si>
+    <t>Overture</t>
+  </si>
+  <si>
+    <t>Millot Echezeaux</t>
+  </si>
+  <si>
+    <t>Petrus</t>
+  </si>
+  <si>
+    <t>Scarecrow</t>
+  </si>
+  <si>
+    <t>Ducru-Beaucaillou</t>
+  </si>
+  <si>
+    <t>Masseto</t>
+  </si>
+  <si>
+    <t>Bond Matriarch</t>
+  </si>
+  <si>
+    <t>Domaine Ponsot</t>
+  </si>
+  <si>
+    <t>Ausone</t>
+  </si>
+  <si>
+    <t>Hundred Acre (Hundred Acre Wraith)</t>
+  </si>
+  <si>
+    <t>Lalande</t>
+  </si>
+  <si>
+    <t>Le Macchiole</t>
+  </si>
+  <si>
+    <t>Scarecrow M. Etain</t>
+  </si>
+  <si>
+    <t>domaine jean grivot</t>
+  </si>
+  <si>
+    <t>Angelus</t>
+  </si>
+  <si>
+    <t>Schrader Cellars</t>
+  </si>
+  <si>
+    <t>Pontet-Canet</t>
+  </si>
+  <si>
+    <t>Grattamacco</t>
+  </si>
+  <si>
+    <t>Bryant Bettina</t>
+  </si>
+  <si>
+    <t>Cheval Blanc</t>
+  </si>
+  <si>
+    <t>Opus One</t>
+  </si>
+  <si>
+    <t>Leoville-Las Cases (use "Las Cases")</t>
+  </si>
+  <si>
+    <t>Argentiera</t>
+  </si>
+  <si>
+    <t>Bryant DB4</t>
+  </si>
+  <si>
+    <t>Lafleur</t>
+  </si>
+  <si>
+    <t>Sine Qua Non</t>
+  </si>
+  <si>
+    <t>Montrose</t>
+  </si>
+  <si>
+    <t>San Leonardo</t>
+  </si>
+  <si>
+    <t>Realm the Bard</t>
+  </si>
+  <si>
+    <t>Pavie</t>
+  </si>
+  <si>
+    <t>Bond</t>
+  </si>
+  <si>
+    <t>Pichon-Longueville Baron (just use "Baron")</t>
+  </si>
+  <si>
+    <t>Luce della Vite</t>
+  </si>
+  <si>
+    <t>The Mascot</t>
+  </si>
+  <si>
+    <t>Figeac</t>
+  </si>
+  <si>
+    <t>Promontory</t>
+  </si>
+  <si>
+    <t>Trotanoy</t>
+  </si>
+  <si>
+    <t>Poggio al Tesoro</t>
+  </si>
+  <si>
+    <t>Branaire ducru</t>
+  </si>
+  <si>
+    <t>Dyquem</t>
+  </si>
+  <si>
+    <t>Sloan</t>
+  </si>
+  <si>
+    <t>Clinet</t>
+  </si>
+  <si>
+    <t>Campo di Sasso</t>
+  </si>
+  <si>
+    <t>Les Forts de Latour</t>
+  </si>
+  <si>
+    <t>Philip Togni</t>
+  </si>
+  <si>
+    <t>L'Eglise Clinet</t>
+  </si>
+  <si>
+    <t>Montepeloso</t>
+  </si>
+  <si>
+    <t>Chateau Lafleur</t>
+  </si>
+  <si>
+    <t>L'Evangile</t>
+  </si>
+  <si>
+    <t>Biserno</t>
+  </si>
+  <si>
+    <t>Arnoux</t>
+  </si>
+  <si>
+    <t>Le Gay</t>
+  </si>
+  <si>
+    <t>Tua Rita</t>
+  </si>
+  <si>
+    <t>Dominus</t>
+  </si>
+  <si>
+    <t>Leoville Poyferre (use "Poyferre")</t>
+  </si>
+  <si>
+    <t>Petrolo</t>
+  </si>
+  <si>
+    <t>Plumpjack</t>
+  </si>
+  <si>
+    <t>Canon</t>
+  </si>
+  <si>
+    <t>Il Poggione</t>
+  </si>
+  <si>
+    <t>Kapscandy</t>
+  </si>
+  <si>
+    <t>Castello di Ama</t>
+  </si>
+  <si>
+    <t>Levy &amp; McClellan</t>
+  </si>
+  <si>
+    <t>Pape Clement</t>
+  </si>
+  <si>
+    <t>Fontodi</t>
+  </si>
+  <si>
+    <t>Odette</t>
+  </si>
+  <si>
+    <t>Haut Bailly</t>
+  </si>
+  <si>
+    <t>Burlotto</t>
+  </si>
+  <si>
+    <t>Montelena</t>
+  </si>
+  <si>
+    <t>Beausejour</t>
+  </si>
+  <si>
+    <t>Verite</t>
+  </si>
+  <si>
+    <t>Peby Faugeres</t>
+  </si>
+  <si>
+    <t>Bella Oaks</t>
+  </si>
+  <si>
+    <t>Aubert</t>
+  </si>
+  <si>
+    <t>Leoville Barton (use "Barton")</t>
+  </si>
+  <si>
+    <t>Talbot</t>
+  </si>
+  <si>
+    <t>Grand Puy Lacoste</t>
+  </si>
+  <si>
+    <t>Rauzan Segla</t>
+  </si>
+  <si>
+    <t>Brane Cantenac</t>
+  </si>
+  <si>
+    <t>Giscours</t>
+  </si>
+  <si>
+    <t>Lascombes</t>
+  </si>
+  <si>
+    <t>Durfort Vivens</t>
+  </si>
+  <si>
+    <t>Malescot St Exupery</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>ITY</t>
+  </si>
+  <si>
+    <t>Bordeaux: Left+Right Bank, SKU contains "BDX:", Region Contains Bordeaux</t>
+  </si>
+  <si>
+    <t>Burgundy : SKU contains "BUR:" and region contains Burgundy</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>California: Region contains California</t>
+  </si>
+  <si>
+    <t>SKU contains "USR:", :USW:"</t>
+  </si>
+  <si>
+    <t>SKU contains "AUS:", region contains Australia</t>
+  </si>
+  <si>
+    <t>SKU contains "SPN", region contains Spain</t>
+  </si>
+  <si>
+    <t>SKU contains "ITY", region contains Italy</t>
+  </si>
+  <si>
+    <t>Left Bank Producers</t>
+  </si>
+  <si>
+    <t>Right Bank Producers</t>
+  </si>
+  <si>
+    <t>Beychevelle</t>
+  </si>
+  <si>
+    <t>Chablis</t>
+  </si>
+  <si>
+    <t>Guigal La Mouline</t>
+  </si>
+  <si>
+    <t>O'Shaughnessy</t>
+  </si>
+  <si>
+    <t>Pingus</t>
+  </si>
+  <si>
+    <t>Branaire Ducru</t>
+  </si>
+  <si>
+    <t>Leflaive</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Marcoux Chateauneuf du Pape</t>
+  </si>
+  <si>
+    <t>Harlan Mascot</t>
+  </si>
+  <si>
+    <t>Pingus Amelia</t>
+  </si>
+  <si>
+    <t>Cos d Estournel</t>
+  </si>
+  <si>
+    <t>Bellevue Mondotte</t>
+  </si>
+  <si>
+    <t>Clos de Tart</t>
+  </si>
+  <si>
+    <t>Chateauneuf du Pape</t>
+  </si>
+  <si>
+    <t>Bryant Estate</t>
+  </si>
+  <si>
+    <t>Ducru Beaucaillou</t>
+  </si>
+  <si>
+    <t>Berliquet</t>
+  </si>
+  <si>
+    <t>Arnoux Vosne Romanee Aux Reignots</t>
+  </si>
+  <si>
+    <t>Duhart Milon</t>
+  </si>
+  <si>
+    <t>Beausejour Duffau Lagarrosse</t>
+  </si>
+  <si>
+    <t>Gloria</t>
+  </si>
+  <si>
+    <t>Beausejour Becot</t>
+  </si>
+  <si>
+    <t>dujac</t>
+  </si>
+  <si>
+    <t>Grand Puy Ducasse</t>
+  </si>
+  <si>
+    <t>Belair Monange</t>
+  </si>
+  <si>
+    <t>rousseau chambertin mazis</t>
+  </si>
+  <si>
+    <t>Hundred Acre</t>
+  </si>
+  <si>
+    <t>domaine dujac</t>
+  </si>
+  <si>
+    <t>Canon La Gaffeliere</t>
+  </si>
+  <si>
+    <t>Haut Bages Liberal</t>
+  </si>
+  <si>
+    <t>Clos Fourtet</t>
+  </si>
+  <si>
+    <t>Haut Batailley</t>
+  </si>
+  <si>
+    <t>Haut Bergey</t>
+  </si>
+  <si>
+    <t>Croix de Labrie</t>
+  </si>
+  <si>
     <t>Haut Brion</t>
   </si>
   <si>
-    <t>Bryant Family</t>
-  </si>
-  <si>
-    <t>Gruaud Larose</t>
-  </si>
-  <si>
-    <t>Tignanello</t>
-  </si>
-  <si>
-    <t>Le Petit Mouton</t>
-  </si>
-  <si>
-    <t>Mouton</t>
-  </si>
-  <si>
-    <t>Dalla Valle</t>
-  </si>
-  <si>
-    <t>Cos d'Estournel</t>
-  </si>
-  <si>
-    <t>Solaia</t>
-  </si>
-  <si>
-    <t>Le Petit Cheval</t>
-  </si>
-  <si>
-    <t>Margaux</t>
-  </si>
-  <si>
-    <t>Colgin Cellars</t>
-  </si>
-  <si>
-    <t>La Mission Haut-Brion</t>
-  </si>
-  <si>
-    <t>Guado al Tasso</t>
-  </si>
-  <si>
-    <t>Overture</t>
-  </si>
-  <si>
-    <t>Petrus</t>
-  </si>
-  <si>
-    <t>Scarecrow</t>
-  </si>
-  <si>
-    <t>Ducru-Beaucaillou</t>
-  </si>
-  <si>
-    <t>Masseto</t>
-  </si>
-  <si>
-    <t>Bond Matriarch</t>
-  </si>
-  <si>
-    <t>Ausone</t>
-  </si>
-  <si>
-    <t>Hundred Acre (Hundred Acre Wraith)</t>
-  </si>
-  <si>
-    <t>Lalande</t>
-  </si>
-  <si>
-    <t>Le Macchiole</t>
-  </si>
-  <si>
-    <t>Scarecrow M. Etain</t>
-  </si>
-  <si>
-    <t>Angelus</t>
-  </si>
-  <si>
-    <t>Schrader Cellars</t>
-  </si>
-  <si>
-    <t>Pontet-Canet</t>
-  </si>
-  <si>
-    <t>Grattamacco</t>
-  </si>
-  <si>
-    <t>Bryant Bettina</t>
-  </si>
-  <si>
-    <t>Cheval Blanc</t>
-  </si>
-  <si>
-    <t>Opus One</t>
-  </si>
-  <si>
-    <t>Leoville-Las Cases (use "Las Cases")</t>
-  </si>
-  <si>
-    <t>Argentiera</t>
-  </si>
-  <si>
-    <t>Bryant DB4</t>
-  </si>
-  <si>
-    <t>Lafleur</t>
-  </si>
-  <si>
-    <t>Sine Qua Non</t>
-  </si>
-  <si>
-    <t>Montrose</t>
-  </si>
-  <si>
-    <t>San Leonardo</t>
-  </si>
-  <si>
-    <t>Realm the Bard</t>
-  </si>
-  <si>
-    <t>Pavie</t>
-  </si>
-  <si>
-    <t>Bond</t>
-  </si>
-  <si>
-    <t>Pichon-Longueville Baron (just use "Baron")</t>
-  </si>
-  <si>
-    <t>Luce della Vite</t>
-  </si>
-  <si>
-    <t>Figeac</t>
-  </si>
-  <si>
-    <t>Promontory</t>
-  </si>
-  <si>
-    <t>Trotanoy</t>
-  </si>
-  <si>
-    <t>Poggio al Tesoro</t>
-  </si>
-  <si>
-    <t>Sloan</t>
-  </si>
-  <si>
-    <t>Clinet</t>
-  </si>
-  <si>
-    <t>Campo di Sasso</t>
-  </si>
-  <si>
-    <t>Philip Togni</t>
-  </si>
-  <si>
-    <t>L'Eglise Clinet</t>
-  </si>
-  <si>
-    <t>Montepeloso</t>
-  </si>
-  <si>
-    <t>Chateau Lafleur</t>
-  </si>
-  <si>
-    <t>L'Evangile</t>
-  </si>
-  <si>
-    <t>Biserno</t>
-  </si>
-  <si>
-    <t>Arnoux</t>
-  </si>
-  <si>
-    <t>Le Gay</t>
-  </si>
-  <si>
-    <t>Tua Rita</t>
-  </si>
-  <si>
-    <t>Dominus</t>
-  </si>
-  <si>
-    <t>Leoville Poyferre (use "Poyferre")</t>
-  </si>
-  <si>
-    <t>Petrolo</t>
-  </si>
-  <si>
-    <t>Plumpjack</t>
-  </si>
-  <si>
-    <t>Canon</t>
-  </si>
-  <si>
-    <t>Il Poggione</t>
-  </si>
-  <si>
-    <t>Les Forts de Latour</t>
-  </si>
-  <si>
-    <t>Castello di Ama</t>
-  </si>
-  <si>
-    <t>Pape Clement</t>
-  </si>
-  <si>
-    <t>Fontodi</t>
-  </si>
-  <si>
-    <t>Haut Bailly</t>
-  </si>
-  <si>
-    <t>Beausejour</t>
-  </si>
-  <si>
-    <t>Peby Faugeres</t>
-  </si>
-  <si>
-    <t>Leoville Barton (use "Barton")</t>
-  </si>
-  <si>
-    <t>Talbot</t>
-  </si>
-  <si>
-    <t>Grand Puy Lacoste</t>
-  </si>
-  <si>
-    <t>Rauzan Segla</t>
-  </si>
-  <si>
-    <t>Brane Cantenac</t>
-  </si>
-  <si>
-    <t>Giscours</t>
-  </si>
-  <si>
-    <t>Lascombes</t>
-  </si>
-  <si>
-    <t>Durfort Vivens</t>
-  </si>
-  <si>
-    <t>Malescot St Exupery</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>US</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>ITY</t>
-  </si>
-  <si>
-    <t>Bordeaux: Left+Right Bank, SKU contains "BDX:", Region Contains Bordeaux</t>
-  </si>
-  <si>
-    <t>Burgundy : SKU contains "BUR:" and region contains Burgundy</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>California: Region contains California</t>
-  </si>
-  <si>
-    <t>SKU contains "USR:", :USW:"</t>
-  </si>
-  <si>
-    <t>SKU contains "AUS:", region contains Australia</t>
-  </si>
-  <si>
-    <t>SKU contains "SPN", region contains Spain</t>
-  </si>
-  <si>
-    <t>SKU contains "ITY", region contains Italy</t>
-  </si>
-  <si>
-    <t>Left Bank Producers</t>
-  </si>
-  <si>
-    <t>Right Bank Producers</t>
-  </si>
-  <si>
-    <t>Beychevelle</t>
-  </si>
-  <si>
-    <t>Chablis</t>
-  </si>
-  <si>
-    <t>Guigal La Mouline</t>
-  </si>
-  <si>
-    <t>Branaire Ducru</t>
-  </si>
-  <si>
-    <t>Leflaive</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Marcoux Chateauneuf du Pape</t>
-  </si>
-  <si>
-    <t>Harlan Mascot</t>
-  </si>
-  <si>
-    <t>Cos d Estournel</t>
-  </si>
-  <si>
-    <t>Bellevue Mondotte</t>
-  </si>
-  <si>
-    <t>Clos de Tart</t>
-  </si>
-  <si>
-    <t>Bryant Estate</t>
-  </si>
-  <si>
-    <t>Ducru Beaucaillou</t>
-  </si>
-  <si>
-    <t>Berliquet</t>
-  </si>
-  <si>
-    <t>Arnoux Vosne Romanee Aux Reignots</t>
-  </si>
-  <si>
-    <t>Duhart Milon</t>
-  </si>
-  <si>
-    <t>Beausejour Duffau Lagarrosse</t>
-  </si>
-  <si>
-    <t>Domaine de la Romanée-Conti (DRC)</t>
-  </si>
-  <si>
-    <t>Gloria</t>
-  </si>
-  <si>
-    <t>Beausejour Becot</t>
-  </si>
-  <si>
-    <t>dujac</t>
-  </si>
-  <si>
-    <t>Grand Puy Ducasse</t>
-  </si>
-  <si>
-    <t>Belair Monange</t>
-  </si>
-  <si>
-    <t>Hundred Acre</t>
-  </si>
-  <si>
-    <t>Canon La Gaffeliere</t>
-  </si>
-  <si>
-    <t>Haut Bages Liberal</t>
-  </si>
-  <si>
-    <t>Clos Fourtet</t>
-  </si>
-  <si>
-    <t>Haut Batailley</t>
-  </si>
-  <si>
-    <t>Haut Bergey</t>
-  </si>
-  <si>
-    <t>Croix de Labrie</t>
-  </si>
-  <si>
     <t>Beringer</t>
   </si>
   <si>
@@ -500,6 +580,9 @@
   </si>
   <si>
     <t>La Conseillante</t>
+  </si>
+  <si>
+    <t>the Mascot</t>
   </si>
   <si>
     <t>Leoville Barton</t>
@@ -623,7 +706,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -636,7 +719,7 @@
       <u/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -644,21 +727,21 @@
       <u/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -683,6 +766,13 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -783,7 +873,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -794,6 +884,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1144,17 +1235,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="39.7109375" customWidth="1"/>
     <col min="2" max="2" width="35.28515625" customWidth="1"/>
     <col min="3" max="3" width="54.42578125" customWidth="1"/>
     <col min="4" max="4" width="49.28515625" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:6" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1170,361 +1262,421 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75">
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.6">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.6">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75">
+      <c r="A5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75">
+      <c r="A6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75">
+      <c r="A7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75">
+      <c r="A8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.6">
+      <c r="A9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.6">
+      <c r="A10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.6">
+      <c r="A11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.6">
+      <c r="A12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75">
+      <c r="A13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75">
+      <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.6">
+      <c r="B15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.6">
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="15.6">
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="15.6">
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="15.6">
+      <c r="B19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="15.6">
+      <c r="B20" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="15.75">
+      <c r="B21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="15.75">
+      <c r="B22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="15.75">
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="15.75">
+      <c r="B24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="15.75">
+      <c r="B25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75">
-      <c r="A5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="26" spans="2:4" ht="15.75">
+      <c r="B26" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75">
-      <c r="A6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75">
-      <c r="A7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.75">
-      <c r="A8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.75">
-      <c r="A9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15.75">
-      <c r="A10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15.75">
-      <c r="A11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.75">
-      <c r="A12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.75">
-      <c r="A13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.75">
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75">
-      <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15.75">
-      <c r="B16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="15.75">
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="15.75">
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="15.75">
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="15.75">
-      <c r="C20" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" ht="15.75">
-      <c r="C21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" ht="15.75">
-      <c r="C22" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="15.75">
-      <c r="C23" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" ht="15.75">
-      <c r="C24" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" ht="15.75">
-      <c r="C25" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" ht="15.75">
-      <c r="C26" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="27" spans="2:4">
       <c r="C27" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="2:4">
       <c r="C28" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="2:4">
       <c r="C29" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="2:4">
       <c r="C30" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="2:4">
       <c r="C31" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="C32" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="3:3">
       <c r="C34" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="3:3">
       <c r="C35" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="3:3" ht="15.75">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3" ht="15.6">
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="3:3" ht="15.75">
+    <row r="37" spans="3:3" ht="15.6">
       <c r="C37" s="3"/>
     </row>
   </sheetData>
@@ -1534,8 +1686,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AC45E4E-988C-4E19-B0DD-F87CDC41132F}">
-  <dimension ref="A1:I52"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:I56"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
     <col min="2" max="2" width="40.28515625" customWidth="1"/>
@@ -1549,593 +1701,688 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="F1" s="17"/>
+      <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="18"/>
       <c r="G1" s="6" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A2" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15.75">
+      <c r="A2" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="5" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
+        <v>130</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="I4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>139</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>143</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="E6" t="s">
-        <v>122</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
       <c r="I8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>155</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>156</v>
       </c>
       <c r="E10" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="I10" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>91</v>
+      </c>
+      <c r="C11" t="s">
+        <v>158</v>
       </c>
       <c r="E11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15">
+      <c r="A13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15">
+      <c r="A14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15">
+      <c r="A15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
         <v>41</v>
       </c>
-      <c r="I11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E12" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>136</v>
-      </c>
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" t="s">
-        <v>137</v>
-      </c>
-      <c r="E14" t="s">
-        <v>56</v>
-      </c>
-      <c r="I14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>138</v>
-      </c>
-      <c r="B15" t="s">
-        <v>64</v>
-      </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="B16" t="s">
-        <v>140</v>
+        <v>164</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I16" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="I17" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="B18" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="E18" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="I18" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="I19" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="E20" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I21" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>178</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>93</v>
       </c>
       <c r="I22" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="B23" t="s">
-        <v>155</v>
+        <v>180</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>181</v>
       </c>
       <c r="I23" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="B24" t="s">
-        <v>157</v>
+        <v>183</v>
+      </c>
+      <c r="E24" t="s">
+        <v>95</v>
       </c>
       <c r="I24" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15">
       <c r="A25" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>186</v>
+      </c>
+      <c r="E25" t="s">
+        <v>98</v>
+      </c>
+      <c r="I25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15">
       <c r="A26" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="B26" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>188</v>
+      </c>
+      <c r="E26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15">
       <c r="A27" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>58</v>
+      </c>
+      <c r="E27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="B28" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>189</v>
+      </c>
+      <c r="E28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
+        <v>190</v>
+      </c>
+      <c r="E29" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="B32" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B34" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="B35" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="B37" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="B39" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="B42" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="B43" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="B45" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="B47" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="B48" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="B49" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="B50" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>193</v>
+        <v>219</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>194</v>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15">
+      <c r="A56" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/Producer - Product Mapping - Copy.xlsx
+++ b/Producer - Product Mapping - Copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grandcruliquidassetscom-my.sharepoint.com/personal/chang_grandcruliquidassets_com/Documents/Desktop/Email campaign dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="562" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A28E9E9C-8F55-42A5-A8E2-0FC99124C128}"/>
+  <xr:revisionPtr revIDLastSave="564" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13905A01-BF65-47DD-AA69-C75B9936232F}"/>
   <bookViews>
-    <workbookView xWindow="47895" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47895" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Producer - Tier" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="292">
   <si>
     <t>First Growth Producers - Flagship</t>
   </si>
@@ -51,7 +51,7 @@
     <t>Napa (not cult wine)</t>
   </si>
   <si>
-    <t>Super Tuscan Producers&amp; Others (I need to research these myself)</t>
+    <t>Super Tuscan Producers&amp; Others</t>
   </si>
   <si>
     <t>Second Label</t>
@@ -505,6 +505,9 @@
   </si>
   <si>
     <t>Tusk</t>
+  </si>
+  <si>
+    <t>Pingus</t>
   </si>
   <si>
     <t>Durfort Vivens</t>
@@ -2002,160 +2005,163 @@
         <v>153</v>
       </c>
     </row>
-    <row r="33" spans="3:4">
+    <row r="33" spans="3:5">
       <c r="C33" t="s">
         <v>154</v>
       </c>
       <c r="D33" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="34" spans="3:4">
+      <c r="E33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5">
       <c r="C34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="35" spans="3:4">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5">
       <c r="C35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D35" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="36" spans="3:4">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5">
       <c r="C36" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D36" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="37" spans="3:4">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5">
       <c r="C37" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D37" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="38" spans="3:4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5">
       <c r="C38" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D38" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="3:4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5">
       <c r="C39" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D39" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="40" spans="3:4">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5">
       <c r="C40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D40" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="41" spans="3:4">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5">
       <c r="C41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D41" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="42" spans="3:4">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5">
       <c r="C42" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D42" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="43" spans="3:4">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5">
       <c r="C43" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D43" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="44" spans="3:4">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5">
       <c r="C44" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D44" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="45" spans="3:4">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5">
       <c r="C45" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="46" spans="3:4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5">
       <c r="C46" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="47" spans="3:4">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="47" spans="3:5">
       <c r="C47" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="48" spans="3:4">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="48" spans="3:5">
       <c r="C48" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49" spans="3:3">
       <c r="C49" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51" spans="3:3">
       <c r="C51" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="3:3">
       <c r="C52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="3:3" ht="15" customHeight="1">
       <c r="C53" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="3:3" ht="15" customHeight="1">
       <c r="C54" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="3:3" ht="15" customHeight="1">
       <c r="C55" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="3:3" ht="15" customHeight="1">
       <c r="C56" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2181,58 +2187,58 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
       <c r="D1" s="13"/>
       <c r="E1" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F1" s="19"/>
       <c r="G1" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="15"/>
@@ -2244,16 +2250,16 @@
     </row>
     <row r="4" spans="1:9" ht="15">
       <c r="A4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -2263,27 +2269,27 @@
         <v>153</v>
       </c>
       <c r="H4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="A5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -2291,12 +2297,12 @@
         <v>147</v>
       </c>
       <c r="I5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B6" t="s">
         <v>108</v>
@@ -2305,15 +2311,15 @@
         <v>69</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I6" t="s">
         <v>18</v>
@@ -2321,16 +2327,16 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
@@ -2344,16 +2350,16 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
@@ -2367,16 +2373,16 @@
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E9" t="s">
         <v>43</v>
@@ -2387,19 +2393,19 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I10" t="s">
         <v>46</v>
@@ -2413,10 +2419,10 @@
         <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E11" t="s">
         <v>57</v>
@@ -2430,7 +2436,7 @@
         <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
@@ -2447,7 +2453,7 @@
     </row>
     <row r="13" spans="1:9" ht="15">
       <c r="A13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B13" t="s">
         <v>63</v>
@@ -2467,7 +2473,7 @@
         <v>120</v>
       </c>
       <c r="B14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" t="s">
         <v>41</v>
@@ -2481,7 +2487,7 @@
     </row>
     <row r="15" spans="1:9" ht="15">
       <c r="A15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B15" t="s">
         <v>87</v>
@@ -2498,10 +2504,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C16" t="s">
         <v>55</v>
@@ -2532,16 +2538,16 @@
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C18" t="s">
         <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I18" t="s">
         <v>94</v>
@@ -2549,10 +2555,10 @@
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C19" t="s">
         <v>81</v>
@@ -2566,16 +2572,16 @@
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C20" t="s">
         <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I20" t="s">
         <v>103</v>
@@ -2583,13 +2589,13 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B21" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C21" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>74</v>
@@ -2600,10 +2606,10 @@
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="A22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C22" t="s">
         <v>96</v>
@@ -2617,16 +2623,16 @@
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="A23" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s">
         <v>127</v>
       </c>
       <c r="C23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I23" t="s">
         <v>114</v>
@@ -2634,24 +2640,24 @@
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E24" t="s">
         <v>66</v>
       </c>
       <c r="I24" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E25" t="s">
         <v>72</v>
@@ -2662,10 +2668,10 @@
     </row>
     <row r="26" spans="1:9" ht="15">
       <c r="A26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E26" t="s">
         <v>78</v>
@@ -2679,7 +2685,7 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E27" t="s">
         <v>83</v>
@@ -2690,10 +2696,10 @@
     </row>
     <row r="28" spans="1:9" ht="15">
       <c r="A28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B28" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E28" t="s">
         <v>88</v>
@@ -2707,7 +2713,7 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E29" t="s">
         <v>93</v>
@@ -2718,7 +2724,7 @@
     </row>
     <row r="30" spans="1:9" ht="15">
       <c r="A30" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
@@ -2735,7 +2741,7 @@
         <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E31" t="s">
         <v>102</v>
@@ -2746,10 +2752,10 @@
     </row>
     <row r="32" spans="1:9" ht="15">
       <c r="A32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E32" t="s">
         <v>106</v>
@@ -2763,7 +2769,7 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E33" t="s">
         <v>110</v>
@@ -2777,7 +2783,7 @@
         <v>116</v>
       </c>
       <c r="B34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E34" t="s">
         <v>113</v>
@@ -2785,13 +2791,13 @@
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B35" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E35" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
@@ -2807,13 +2813,13 @@
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E37" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
@@ -2821,7 +2827,7 @@
         <v>145</v>
       </c>
       <c r="B38" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E38" t="s">
         <v>121</v>
@@ -2829,10 +2835,10 @@
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E39" t="s">
         <v>125</v>
@@ -2840,13 +2846,13 @@
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B40" t="s">
         <v>42</v>
       </c>
       <c r="E40" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
@@ -2854,7 +2860,7 @@
         <v>139</v>
       </c>
       <c r="B41" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E41" t="s">
         <v>129</v>
@@ -2862,21 +2868,21 @@
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B42" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E42" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B43" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E43" t="s">
         <v>134</v>
@@ -2884,10 +2890,10 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B44" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E44" t="s">
         <v>137</v>
@@ -2895,10 +2901,10 @@
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B45" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E45" t="s">
         <v>140</v>
@@ -2917,7 +2923,7 @@
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B47" t="s">
         <v>119</v>
@@ -2931,21 +2937,21 @@
         <v>151</v>
       </c>
       <c r="B48" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15">
       <c r="A49" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B49" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E49" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15">
@@ -2953,43 +2959,43 @@
         <v>154</v>
       </c>
       <c r="B50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15">
       <c r="A51" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>124</v>
       </c>
       <c r="E51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15">
       <c r="A52" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B52" t="s">
         <v>108</v>
       </c>
       <c r="E52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15">
       <c r="A53" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15">
@@ -3016,18 +3022,18 @@
     </row>
     <row r="56" spans="1:5" ht="15">
       <c r="A56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B56" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E56" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15">
       <c r="A57" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B57" t="s">
         <v>119</v>
@@ -3038,29 +3044,29 @@
     </row>
     <row r="58" spans="1:5" ht="15">
       <c r="A58" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B58" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E58" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15">
       <c r="A59" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B59" t="s">
         <v>97</v>
       </c>
       <c r="E59" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15">
       <c r="A60" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B60" t="s">
         <v>40</v>
@@ -3071,7 +3077,7 @@
     </row>
     <row r="61" spans="1:5" ht="15">
       <c r="A61" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -3079,7 +3085,7 @@
     </row>
     <row r="62" spans="1:5" ht="15">
       <c r="A62" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E62" t="s">
         <v>12</v>
@@ -3087,7 +3093,7 @@
     </row>
     <row r="63" spans="1:5" ht="15">
       <c r="A63" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E63" t="s">
         <v>24</v>
@@ -3095,20 +3101,20 @@
     </row>
     <row r="64" spans="1:5" ht="15">
       <c r="A64" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E64" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="15">
       <c r="A65" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="15">
       <c r="A66" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="15">

--- a/Producer - Product Mapping - Copy.xlsx
+++ b/Producer - Product Mapping - Copy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30128"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grandcruliquidassetscom-my.sharepoint.com/personal/chang_grandcruliquidassets_com/Documents/Desktop/Email campaign dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="564" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13905A01-BF65-47DD-AA69-C75B9936232F}"/>
+  <xr:revisionPtr revIDLastSave="587" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F6A15DD-19AD-46B9-A60A-6D6BD49837FC}"/>
   <bookViews>
-    <workbookView xWindow="47895" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47895" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Producer - Tier" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="294">
   <si>
     <t>First Growth Producers - Flagship</t>
   </si>
@@ -516,6 +516,9 @@
     <t>Ulysses</t>
   </si>
   <si>
+    <t>Jaboulet</t>
+  </si>
+  <si>
     <t>Malescot St Exupery</t>
   </si>
   <si>
@@ -528,6 +531,9 @@
     <t>Caymus Special Select</t>
   </si>
   <si>
+    <t>cavallotto</t>
+  </si>
+  <si>
     <t>Chapoutier</t>
   </si>
   <si>
@@ -579,9 +585,15 @@
     <t>Krug</t>
   </si>
   <si>
+    <t>Pavie Macquin</t>
+  </si>
+  <si>
     <t>Cristal</t>
   </si>
   <si>
+    <t>chappellet</t>
+  </si>
+  <si>
     <t>Ducru Beaucaillou</t>
   </si>
   <si>
@@ -612,6 +624,9 @@
     <t>Arnoux</t>
   </si>
   <si>
+    <t>Smith Haut Lafitte</t>
+  </si>
+  <si>
     <t>France</t>
   </si>
   <si>
@@ -624,7 +639,7 @@
     <t>Spain</t>
   </si>
   <si>
-    <t>ITY</t>
+    <t>Italy</t>
   </si>
   <si>
     <t>Bordeaux: Left+Right Bank, SKU contains "BDX:", Region Contains Bordeaux</t>
@@ -684,9 +699,6 @@
     <t>Harlan Mascot</t>
   </si>
   <si>
-    <t>dell Ornellaia</t>
-  </si>
-  <si>
     <t>Cos d Estournel</t>
   </si>
   <si>
@@ -838,12 +850,6 @@
   </si>
   <si>
     <t>Combo - Peter Michael + Morlet</t>
-  </si>
-  <si>
-    <t>Pavie Macquin</t>
-  </si>
-  <si>
-    <t>Smith Haut Lafitte</t>
   </si>
   <si>
     <t>Petit Village</t>
@@ -1455,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -2023,145 +2029,165 @@
       <c r="D34" t="s">
         <v>158</v>
       </c>
+      <c r="E34" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="35" spans="3:5">
       <c r="C35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="E35" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="3:5">
       <c r="C36" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D36" t="s">
-        <v>162</v>
+        <v>163</v>
+      </c>
+      <c r="E36" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="3:5">
       <c r="C37" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D37" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="3:5">
       <c r="C38" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D38" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="3:5">
       <c r="C39" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D39" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="3:5">
       <c r="C40" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D40" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="3:5">
       <c r="C41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D41" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="3:5">
       <c r="C42" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D42" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="43" spans="3:5">
       <c r="C43" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D43" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="3:5">
       <c r="C44" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D44" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45" spans="3:5">
       <c r="C45" t="s">
-        <v>179</v>
+        <v>181</v>
+      </c>
+      <c r="D45" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="3:5">
       <c r="C46" t="s">
-        <v>180</v>
+        <v>183</v>
+      </c>
+      <c r="D46" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="47" spans="3:5">
       <c r="C47" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="3:5">
       <c r="C48" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="49" spans="3:3">
       <c r="C49" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="3:3">
       <c r="C51" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52" spans="3:3">
       <c r="C52" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="3:3" ht="15" customHeight="1">
       <c r="C53" s="7" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" spans="3:3" ht="15" customHeight="1">
       <c r="C54" s="7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="3:3" ht="15" customHeight="1">
       <c r="C55" s="9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="3:3" ht="15" customHeight="1">
       <c r="C56" t="s">
-        <v>190</v>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3" ht="15" customHeight="1">
+      <c r="C57" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -2171,7 +2197,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AC45E4E-988C-4E19-B0DD-F87CDC41132F}">
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
@@ -2187,58 +2213,58 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="11" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
       <c r="D1" s="13"/>
       <c r="E1" s="18" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F1" s="19"/>
       <c r="G1" s="6" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="16" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="17" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.6">
       <c r="A3" s="5" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="15"/>
@@ -2250,16 +2276,16 @@
     </row>
     <row r="4" spans="1:9" ht="15">
       <c r="A4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D4" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -2269,27 +2295,27 @@
         <v>153</v>
       </c>
       <c r="H4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="I4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="A5" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D5" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -2297,12 +2323,12 @@
         <v>147</v>
       </c>
       <c r="I5" t="s">
-        <v>215</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B6" t="s">
         <v>108</v>
@@ -2311,15 +2337,15 @@
         <v>69</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E6" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I6" t="s">
         <v>18</v>
@@ -2327,16 +2353,16 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
@@ -2350,16 +2376,16 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B8" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
@@ -2373,16 +2399,16 @@
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B9" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E9" t="s">
         <v>43</v>
@@ -2393,19 +2419,19 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B10" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E10" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I10" t="s">
         <v>46</v>
@@ -2419,10 +2445,10 @@
         <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D11" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E11" t="s">
         <v>57</v>
@@ -2436,7 +2462,7 @@
         <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
@@ -2453,13 +2479,16 @@
     </row>
     <row r="13" spans="1:9" ht="15">
       <c r="A13" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B13" t="s">
         <v>63</v>
       </c>
       <c r="C13" t="s">
         <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>159</v>
       </c>
       <c r="E13" t="s">
         <v>45</v>
@@ -2473,7 +2502,7 @@
         <v>120</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C14" t="s">
         <v>41</v>
@@ -2487,7 +2516,7 @@
     </row>
     <row r="15" spans="1:9" ht="15">
       <c r="A15" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B15" t="s">
         <v>87</v>
@@ -2504,10 +2533,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B16" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C16" t="s">
         <v>55</v>
@@ -2538,16 +2567,16 @@
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B18" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C18" t="s">
         <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I18" t="s">
         <v>94</v>
@@ -2555,10 +2584,10 @@
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B19" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C19" t="s">
         <v>81</v>
@@ -2572,16 +2601,16 @@
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B20" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C20" t="s">
         <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I20" t="s">
         <v>103</v>
@@ -2589,13 +2618,13 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B21" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C21" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>74</v>
@@ -2606,10 +2635,10 @@
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="A22" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B22" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C22" t="s">
         <v>96</v>
@@ -2623,16 +2652,16 @@
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="A23" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s">
         <v>127</v>
       </c>
       <c r="C23" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I23" t="s">
         <v>114</v>
@@ -2640,24 +2669,24 @@
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E24" t="s">
         <v>66</v>
       </c>
       <c r="I24" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E25" t="s">
         <v>72</v>
@@ -2668,10 +2697,10 @@
     </row>
     <row r="26" spans="1:9" ht="15">
       <c r="A26" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E26" t="s">
         <v>78</v>
@@ -2685,7 +2714,7 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E27" t="s">
         <v>83</v>
@@ -2696,10 +2725,10 @@
     </row>
     <row r="28" spans="1:9" ht="15">
       <c r="A28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E28" t="s">
         <v>88</v>
@@ -2713,7 +2742,7 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E29" t="s">
         <v>93</v>
@@ -2724,7 +2753,7 @@
     </row>
     <row r="30" spans="1:9" ht="15">
       <c r="A30" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s">
         <v>101</v>
@@ -2741,7 +2770,7 @@
         <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E31" t="s">
         <v>102</v>
@@ -2752,10 +2781,10 @@
     </row>
     <row r="32" spans="1:9" ht="15">
       <c r="A32" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E32" t="s">
         <v>106</v>
@@ -2769,7 +2798,7 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E33" t="s">
         <v>110</v>
@@ -2783,21 +2812,27 @@
         <v>116</v>
       </c>
       <c r="B34" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E34" t="s">
         <v>113</v>
       </c>
+      <c r="I34" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E35" t="s">
-        <v>264</v>
+        <v>268</v>
+      </c>
+      <c r="I35" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
@@ -2813,13 +2848,13 @@
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E37" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
@@ -2827,7 +2862,7 @@
         <v>145</v>
       </c>
       <c r="B38" t="s">
-        <v>267</v>
+        <v>182</v>
       </c>
       <c r="E38" t="s">
         <v>121</v>
@@ -2835,10 +2870,10 @@
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>268</v>
+        <v>195</v>
       </c>
       <c r="B39" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E39" t="s">
         <v>125</v>
@@ -2846,13 +2881,13 @@
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B40" t="s">
         <v>42</v>
       </c>
       <c r="E40" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
@@ -2860,7 +2895,7 @@
         <v>139</v>
       </c>
       <c r="B41" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E41" t="s">
         <v>129</v>
@@ -2868,21 +2903,21 @@
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B42" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E42" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B43" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E43" t="s">
         <v>134</v>
@@ -2890,10 +2925,10 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B44" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E44" t="s">
         <v>137</v>
@@ -2901,10 +2936,10 @@
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B45" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E45" t="s">
         <v>140</v>
@@ -2923,7 +2958,7 @@
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B47" t="s">
         <v>119</v>
@@ -2937,21 +2972,21 @@
         <v>151</v>
       </c>
       <c r="B48" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E48" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15">
       <c r="A49" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B49" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E49" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15">
@@ -2959,43 +2994,43 @@
         <v>154</v>
       </c>
       <c r="B50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E50" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15">
       <c r="A51" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>124</v>
       </c>
       <c r="E51" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15">
       <c r="A52" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B52" t="s">
         <v>108</v>
       </c>
       <c r="E52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15">
       <c r="A53" s="8" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B53" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E53" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15">
@@ -3022,18 +3057,18 @@
     </row>
     <row r="56" spans="1:5" ht="15">
       <c r="A56" t="s">
+        <v>191</v>
+      </c>
+      <c r="B56" t="s">
         <v>187</v>
       </c>
-      <c r="B56" t="s">
-        <v>183</v>
-      </c>
       <c r="E56" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15">
       <c r="A57" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B57" t="s">
         <v>119</v>
@@ -3044,10 +3079,10 @@
     </row>
     <row r="58" spans="1:5" ht="15">
       <c r="A58" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B58" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E58" t="s">
         <v>158</v>
@@ -3055,18 +3090,18 @@
     </row>
     <row r="59" spans="1:5" ht="15">
       <c r="A59" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B59" t="s">
         <v>97</v>
       </c>
       <c r="E59" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15">
       <c r="A60" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B60" t="s">
         <v>40</v>
@@ -3077,7 +3112,10 @@
     </row>
     <row r="61" spans="1:5" ht="15">
       <c r="A61" t="s">
-        <v>290</v>
+        <v>292</v>
+      </c>
+      <c r="B61" t="s">
+        <v>195</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -3085,7 +3123,7 @@
     </row>
     <row r="62" spans="1:5" ht="15">
       <c r="A62" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E62" t="s">
         <v>12</v>
@@ -3093,7 +3131,7 @@
     </row>
     <row r="63" spans="1:5" ht="15">
       <c r="A63" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E63" t="s">
         <v>24</v>
@@ -3101,35 +3139,46 @@
     </row>
     <row r="64" spans="1:5" ht="15">
       <c r="A64" t="s">
+        <v>192</v>
+      </c>
+      <c r="E64" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15">
+      <c r="A65" t="s">
         <v>188</v>
       </c>
-      <c r="E64" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" ht="15">
-      <c r="A65" t="s">
+      <c r="E65" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15">
+      <c r="A66" t="s">
+        <v>189</v>
+      </c>
+      <c r="E66" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="15">
-      <c r="A66" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" ht="15">
+    <row r="67" spans="1:5" ht="15">
       <c r="A67" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/Producer - Product Mapping - Copy.xlsx
+++ b/Producer - Product Mapping - Copy.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1734,6 +1734,11 @@
           <t>Ducru Beaucaillou</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Bevan Cellars</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="14.5" customHeight="1">
       <c r="C48" t="inlineStr">
@@ -1802,6 +1807,27 @@
       <c r="C57" t="inlineStr">
         <is>
           <t>Smith Haut Lafitte</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Raya</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Certan de May</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
     </row>
@@ -2290,6 +2316,11 @@
           <t>Millot Echezeaux</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Raya</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Bond</t>
@@ -3239,6 +3270,11 @@
           <t>Léoville Poyferré</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Certan de May</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Harlan Estate</t>
@@ -3251,6 +3287,11 @@
           <t>Combo - Barton + Poyferre</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Larcis Ducasse</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>Harlan Maiden</t>
@@ -3309,6 +3350,11 @@
       <c r="A67" t="inlineStr">
         <is>
           <t>beychevelle</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Bevan Cellars</t>
         </is>
       </c>
     </row>

--- a/Producer - Product Mapping - Copy.xlsx
+++ b/Producer - Product Mapping - Copy.xlsx
@@ -1420,6 +1420,11 @@
           <t>Gaja</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rayas</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15.5" customHeight="1">
       <c r="C26" s="2" t="inlineStr">
@@ -1619,6 +1624,11 @@
           <t>Morlet</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Clos Erasmus</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="14.5" customHeight="1">
       <c r="C38" t="inlineStr">
@@ -1744,6 +1754,11 @@
       <c r="C48" t="inlineStr">
         <is>
           <t>La Mission Haut Brion</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Nine Suns</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2113,11 @@
       </c>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Clos Erasmus</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>Solaia</t>
@@ -2348,6 +2367,11 @@
           <t>Domaine Ponsot</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Rayas</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>Promontory</t>
@@ -3362,6 +3386,11 @@
       <c r="A68" t="inlineStr">
         <is>
           <t>Carruades de Lafite</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Nine Suns</t>
         </is>
       </c>
     </row>

--- a/Producer - Product Mapping - Copy.xlsx
+++ b/Producer - Product Mapping - Copy.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1505,11 +1505,6 @@
           <t>Marcassin</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Vega Sicilia</t>
-        </is>
-      </c>
     </row>
     <row r="31" ht="14.5" customHeight="1">
       <c r="C31" t="inlineStr">
@@ -1843,6 +1838,13 @@
       <c r="C60" t="inlineStr">
         <is>
           <t>Larcis Ducasse</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Vega Sicilia</t>
         </is>
       </c>
     </row>

--- a/Producer - Product Mapping - Copy.xlsx
+++ b/Producer - Product Mapping - Copy.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1845,6 +1845,13 @@
       <c r="C61" t="inlineStr">
         <is>
           <t>Vega Sicilia</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Le Dome</t>
         </is>
       </c>
     </row>
@@ -3330,6 +3337,11 @@
           <t>Ducru Beaucaillou</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Le Dome</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>Philip Togni</t>
